--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N91_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.159957861215488</v>
+        <v>1.163493152447517</v>
       </c>
       <c r="D2" t="n">
-        <v>3.266331452586578</v>
+        <v>0.5307788610453189</v>
       </c>
       <c r="E2" t="n">
-        <v>8.887185658872529</v>
+        <v>1.444167669566786</v>
       </c>
       <c r="F2" t="n">
-        <v>24.88659772048108</v>
+        <v>4.044072129578176</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.45426261703496</v>
+        <v>4.623817675268182</v>
       </c>
       <c r="D3" t="n">
-        <v>14.83126789902953</v>
+        <v>2.410081033592299</v>
       </c>
       <c r="E3" t="n">
-        <v>8.887185658872529</v>
+        <v>1.444167669566786</v>
       </c>
       <c r="F3" t="n">
-        <v>24.88659772048108</v>
+        <v>4.044072129578176</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.72069378562011</v>
+        <v>2.879612740163268</v>
       </c>
       <c r="D4" t="n">
-        <v>9.538504658950536</v>
+        <v>1.550007007079462</v>
       </c>
       <c r="E4" t="n">
-        <v>8.887185658872529</v>
+        <v>1.444167669566786</v>
       </c>
       <c r="F4" t="n">
-        <v>24.88659772048108</v>
+        <v>4.044072129578176</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.68393569700651</v>
+        <v>4.661139550763559</v>
       </c>
       <c r="D5" t="n">
-        <v>65.90227172406782</v>
+        <v>10.70911915516102</v>
       </c>
       <c r="E5" t="n">
-        <v>8.887185658872529</v>
+        <v>1.444167669566786</v>
       </c>
       <c r="F5" t="n">
-        <v>24.88659772048108</v>
+        <v>4.044072129578176</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
